--- a/public/BgtSeatUploader.xlsx
+++ b/public/BgtSeatUploader.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>LOC CODE</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>ACTIVE</t>
+  </si>
+  <si>
+    <t>SUB DEPT 1</t>
+  </si>
+  <si>
+    <t>SUB DEPT 2</t>
+  </si>
+  <si>
+    <t>SUB DEPT 3</t>
   </si>
 </sst>
 </file>
@@ -412,10 +421,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EDF95CB-EC4F-47B0-B9BD-43B4F8DC0304}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -437,9 +446,18 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8831" xr:uid="{7EDF95CB-EC4F-47B0-B9BD-43B4F8DC0304}"/>
+  <autoFilter ref="A1:J8831" xr:uid="{7EDF95CB-EC4F-47B0-B9BD-43B4F8DC0304}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>